--- a/resources/UserDetails.xlsx
+++ b/resources/UserDetails.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Email</t>
   </si>
@@ -51,6 +51,12 @@
   </si>
   <si>
     <t>BobetteKreiger@yopmail.com</t>
+  </si>
+  <si>
+    <t>AdamZulauf@yopmail.com</t>
+  </si>
+  <si>
+    <t>AlejandroPriceDVM@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -95,7 +101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -163,6 +169,26 @@
         <v>12</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
